--- a/docs/oc-regiones/gas-licuado-de-petroleo/region-de-magallanes-y-de-la-antartica.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/region-de-magallanes-y-de-la-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1116007-110-CM26</t>
+          <t>1536-192-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2794.21</v>
+        <v>3747.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>855-128-CM26</t>
+          <t>3595-297-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>335.31</v>
+        <v>1375.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3268-514-CM26</t>
+          <t>1536-195-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>781.76</v>
+        <v>820.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3409-152-CM26</t>
+          <t>1233613-1235-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.101.455-4</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>938.49</v>
+        <v>1360.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1069-96-CM26</t>
+          <t>1536-209-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3404.24</v>
+        <v>4842.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>855-138-CM26</t>
+          <t>3595-358-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>69.61</v>
+        <v>1262.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3704-233-CM26</t>
+          <t>4589-407-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>762.85</v>
+        <v>1694.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1233613-1543-CM26</t>
+          <t>1536-228-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5721.41</v>
+        <v>2348.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233613-1523-CM26</t>
+          <t>1536-227-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1423.79</v>
+        <v>2653.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>855-137-CM26</t>
+          <t>4589-451-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>502.53</v>
+        <v>2062.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079445-512-CM26</t>
+          <t>3595-422-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1434.87</v>
+        <v>1186.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233613-1573-CM26</t>
+          <t>3595-430-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1824.6</v>
+        <v>1635.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>855-141-CM26</t>
+          <t>1536-246-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>347.82</v>
+        <v>4890.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1038-195-CM26</t>
+          <t>1233613-1404-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5351.13</v>
+        <v>1314.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3595-334-CM26</t>
+          <t>1536-256-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2004.13</v>
+        <v>4089.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3704-237-CM26</t>
+          <t>4589-490-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1434.8</v>
+        <v>1942.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4589-366-CM26</t>
+          <t>3595-490-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12912.35</v>
+        <v>1295.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3595-333-CM26</t>
+          <t>4589-519-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1547.35</v>
+        <v>1760.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1470-35-CM26</t>
+          <t>1536-288-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>224.78</v>
+        <v>1562.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3187-294-CM26</t>
+          <t>1536-289-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.102.041-4</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1071.05</v>
+        <v>1875.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>796297-73-CM26</t>
+          <t>1116007-110-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>320.99</v>
+        <v>2794.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1470-34-CM26</t>
+          <t>855-128-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>449.56</v>
+        <v>335.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>855-142-CM26</t>
+          <t>3409-152-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.101.455-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>668.53</v>
+        <v>938.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>855-143-CM26</t>
+          <t>3268-514-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>344.74</v>
+        <v>781.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1038-208-CM26</t>
+          <t>1233613-1523-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2917.17</v>
+        <v>1423.79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1233613-1648-CM26</t>
+          <t>1233613-1543-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2648.96</v>
+        <v>5721.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1233613-1649-CM26</t>
+          <t>855-137-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5342.43</v>
+        <v>502.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>855-144-CM26</t>
+          <t>855-138-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>424.72</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3409-177-CM26</t>
+          <t>1069-96-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.101.455-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1575.71</v>
+        <v>3404.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1079445-564-CM26</t>
+          <t>3704-233-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1313.09</v>
+        <v>762.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>902977-21-CM26</t>
+          <t>1079445-512-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>132.68</v>
+        <v>1434.87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5147-253-CM26</t>
+          <t>1038-195-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1326.8</v>
+        <v>5351.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1116007-122-CM26</t>
+          <t>1233613-1573-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2631.48</v>
+        <v>1824.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1536-175-CM26</t>
+          <t>855-141-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5310.49</v>
+        <v>347.82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>855-145-CM26</t>
+          <t>3704-237-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>315.72</v>
+        <v>1434.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3595-348-CM26</t>
+          <t>4589-366-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1278.43</v>
+        <v>12912.35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>958479-233-CM26</t>
+          <t>3595-333-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.980.720-0</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3107.23</v>
+        <v>1547.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3704-257-CM26</t>
+          <t>3595-334-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,22 +2786,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1425.45</v>
+        <v>2004.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079445-575-CM26</t>
+          <t>796297-73-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1336.36</v>
+        <v>320.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3617-103-CM26</t>
+          <t>1470-34-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>32664.37</v>
+        <v>449.56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1233613-1713-CM26</t>
+          <t>1470-35-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1316.4</v>
+        <v>224.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>855-147-CM26</t>
+          <t>3187-294-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.102.041-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>259.98</v>
+        <v>1071.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>855-148-CM26</t>
+          <t>855-142-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3131,6 +3131,1226 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
+        <v>668.53</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>855-143-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>344.74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1038-208-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>2917.17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>855-144-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>424.72</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1233613-1649-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.980.960-2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Magallanes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>5342.43</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1233613-1648-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.980.960-2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Magallanes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>2648.96</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3409-177-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.101.455-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1575.71</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1079445-564-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60.505.628-8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>1313.09</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1116007-122-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>2631.48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5147-253-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.251.600-1</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>1326.8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>902977-21-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.251.600-1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>132.68</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1536-175-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.511.123-8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>5310.49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>855-145-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>315.72</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3595-348-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.251.400-9</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>1278.43</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>958479-233-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.980.720-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>3107.23</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3704-257-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.254.400-5</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>1425.45</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1079445-575-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>60.505.628-8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>1336.36</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3617-103-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>32664.37</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1233613-1713-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.980.960-2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Magallanes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>1316.4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>855-147-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>259.98</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>855-148-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>655.42</v>
       </c>
     </row>
